--- a/Result/profitability/1218.xlsx
+++ b/Result/profitability/1218.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.34875</v>
+        <v>0.03750000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>17.345</v>
+        <v>16.5875</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,13 +780,13 @@
         <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30125</v>
+        <v>0.02875000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>16.95375</v>
+        <v>16.6425</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,13 +798,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.30625</v>
+        <v>0.01750000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>16.50375</v>
+        <v>16.18625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>-0.82</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1575</v>
+        <v>-0.12125</v>
       </c>
       <c r="N5" t="n">
-        <v>15.08625</v>
+        <v>14.60125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.14</v>
+        <v>-0.15375</v>
       </c>
       <c r="N6" t="n">
-        <v>14.65125</v>
+        <v>14.0775</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.12375</v>
+        <v>-0.18375</v>
       </c>
       <c r="N7" t="n">
-        <v>15.02875</v>
+        <v>14.745</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1</v>
+        <v>-0.1825</v>
       </c>
       <c r="N8" t="n">
-        <v>14.5675</v>
+        <v>14.2025</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06000000000000001</v>
+        <v>0.06000000000000002</v>
       </c>
       <c r="N9" t="n">
         <v>14.8675</v>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05125000000000001</v>
+        <v>0.05125000000000002</v>
       </c>
       <c r="N11" t="n">
         <v>15.07625</v>
@@ -1901,7 +1901,7 @@
         <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06625</v>
+        <v>0.06625000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>14.5975</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2381</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2042</v>
+      </c>
+      <c r="E75" t="n">
+        <v>339</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-218</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-707</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-924</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-944</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.09500000000000003</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.31375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-7.0625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1703617269544924</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.689655172413794</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.880000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2143646408839779</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
